--- a/app/src/main/java/tps/tp1/salida/reporte.xlsx
+++ b/app/src/main/java/tps/tp1/salida/reporte.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Padron</t>
   </si>
@@ -32,22 +32,25 @@
     <t>Estado</t>
   </si>
   <si>
+    <t>Bruno Ferrari</t>
+  </si>
+  <si>
+    <t>CON_DEUDA</t>
+  </si>
+  <si>
+    <t>Ana Gomez</t>
+  </si>
+  <si>
     <t>Diego Ruiz</t>
   </si>
   <si>
-    <t>CON_DEUDA</t>
-  </si>
-  <si>
-    <t>Bruno Ferrari</t>
-  </si>
-  <si>
-    <t>Ana Gomez</t>
+    <t>Elena Sosa</t>
+  </si>
+  <si>
+    <t>Carla Nunez</t>
   </si>
   <si>
     <t>AL_DIA</t>
-  </si>
-  <si>
-    <t>Elena Sosa</t>
   </si>
 </sst>
 </file>
@@ -101,7 +104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.328125" customWidth="true" bestFit="true"/>
@@ -134,19 +137,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n" s="0">
-        <v>40555.0</v>
+        <v>39876.0</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>6</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>1200.0</v>
+        <v>3600.0</v>
       </c>
       <c r="F2" t="s" s="0">
         <v>7</v>
@@ -154,19 +157,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n" s="0">
-        <v>39876.0</v>
+        <v>41234.0</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>8</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>5.0</v>
+        <v>23.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>750.0</v>
+        <v>3450.0</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>7</v>
@@ -174,22 +177,22 @@
     </row>
     <row r="4">
       <c r="A4" t="n" s="0">
-        <v>41234.0</v>
+        <v>40555.0</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>9</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>0.0</v>
+        <v>42.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>0.0</v>
+        <v>3300.0</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -197,19 +200,39 @@
         <v>43310.0</v>
       </c>
       <c r="B5" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>1500.0</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>42001.0</v>
+      </c>
+      <c r="B6" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="C5" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="D5" t="n" s="0">
+      <c r="C6" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D6" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E5" t="n" s="0">
+      <c r="E6" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="F5" t="s" s="0">
-        <v>10</v>
+      <c r="F6" t="s" s="0">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
